--- a/Telecomunicazioni/led_resistenza.xlsx
+++ b/Telecomunicazioni/led_resistenza.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\Desktop\scuola\Telecomunicazioni\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102FC290-512B-4DD1-B0F0-FFDFDE29AEE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5167B34-2990-4719-8AA3-22AF48868A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3DF9D497-AA97-496A-AC35-3E4527FFDC14}"/>
+    <workbookView xWindow="6870" yWindow="1935" windowWidth="21600" windowHeight="11295" xr2:uid="{3DF9D497-AA97-496A-AC35-3E4527FFDC14}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>OHM</t>
   </si>
@@ -50,6 +50,9 @@
   <si>
     <t>MISURA</t>
   </si>
+  <si>
+    <t>Voltaggio Arduino</t>
+  </si>
 </sst>
 </file>
 
@@ -64,15 +67,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -80,12 +89,39 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -118,6 +154,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mj-lt"/>
+                <a:ea typeface="+mj-ea"/>
+                <a:cs typeface="+mj-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>GRAFICO</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -131,16 +192,16 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="2000" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:latin typeface="+mj-lt"/>
+              <a:ea typeface="+mj-ea"/>
+              <a:cs typeface="+mj-cs"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="it-IT"/>
@@ -149,19 +210,9 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="4.3779383741415885E-2"/>
-          <c:y val="7.0137328339575547E-2"/>
-          <c:w val="0.92283248840470289"/>
-          <c:h val="0.87992509363295879"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -178,28 +229,18 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="25400" cap="flat" cmpd="dbl" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent1">
+                  <a:alpha val="50000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
           <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
+            <c:symbol val="none"/>
           </c:marker>
           <c:xVal>
             <c:numRef>
@@ -399,10 +440,10 @@
               </c:numCache>
             </c:numRef>
           </c:yVal>
-          <c:smooth val="1"/>
+          <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FECD-4C66-BA8B-2886C5E9BF23}"/>
+              <c16:uniqueId val="{00000000-3B2A-435F-921B-C9FC9123573F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -414,11 +455,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="1005115119"/>
-        <c:axId val="1005117615"/>
+        <c:axId val="1753327520"/>
+        <c:axId val="1753327936"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="1005115119"/>
+        <c:axId val="1753327520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -438,6 +479,75 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="it-IT"/>
+                  <a:t>V</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -447,11 +557,136 @@
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="it-IT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1753327936"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1753327936"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="it-IT"/>
+                  <a:t>I</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="it-IT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -475,69 +710,7 @@
             <a:endParaRPr lang="it-IT"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1005117615"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="1005117615"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="it-IT"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1005115119"/>
+        <c:crossAx val="1753327520"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -634,7 +807,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="243">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -645,7 +818,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -661,21 +834,24 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="900" b="0" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -691,7 +867,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -711,22 +887,17 @@
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -735,37 +906,49 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="25400" cap="flat" cmpd="dbl" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
@@ -775,22 +958,26 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:ln w="34925" cap="flat" cmpd="dbl" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="75000"/>
+            <a:alpha val="70000"/>
+          </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
@@ -820,15 +1007,13 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -838,7 +1023,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -847,14 +1032,13 @@
           <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -863,17 +1047,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -882,14 +1066,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -901,21 +1085,15 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -934,7 +1112,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -953,17 +1131,17 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="50000"/>
             <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
+        <a:prstDash val="dash"/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -972,17 +1150,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -1003,7 +1180,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
@@ -1011,7 +1188,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -1024,6 +1201,17 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -1031,10 +1219,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
@@ -1049,17 +1237,17 @@
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
+    <cs:fontRef idx="major">
       <a:schemeClr val="tx1">
         <a:lumMod val="65000"/>
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="2000" kern="1200" spc="0" normalizeH="0" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
+      <cs:styleClr val="0"/>
     </cs:lnRef>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -1067,49 +1255,18 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="38100" cap="rnd" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="75000"/>
+            <a:alpha val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
+  </cs:trendline>
+  <cs:trendlineLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
@@ -1119,32 +1276,48 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="0" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -1153,23 +1326,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>265043</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>66261</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>184896</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>32496</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3EAC4490-D05B-4F03-BDAE-414136777DA9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39C81B63-1DAE-4056-8B45-852CA87D1068}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1487,607 +1660,619 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5F749FF-7FC2-492B-949C-BEA78F376BBB}">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A3:E36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="C4" s="1">
+        <v>0.44</v>
+      </c>
+      <c r="D4" s="1">
+        <f>$A$36-C4</f>
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" ref="E4:E32" si="0">D4/B4</f>
+        <v>0.91199999999999992</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0.81</v>
+      </c>
+      <c r="D5" s="1">
+        <f>$A$36-C5</f>
+        <v>4.1899999999999995</v>
+      </c>
+      <c r="E5" s="1">
+        <f t="shared" si="0"/>
+        <v>0.41899999999999993</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="D6" s="1">
+        <f>$A$36-C6</f>
+        <v>3.87</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="0"/>
+        <v>0.19350000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
+      <c r="B7" s="1">
+        <v>50</v>
+      </c>
+      <c r="C7" s="1">
+        <v>1.64</v>
+      </c>
+      <c r="D7" s="1">
+        <f>$A$36-C7</f>
+        <v>3.3600000000000003</v>
+      </c>
+      <c r="E7" s="1">
+        <f t="shared" si="0"/>
+        <v>6.720000000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>5</v>
       </c>
-      <c r="C4">
-        <v>0.44</v>
-      </c>
-      <c r="D4">
-        <f>$A$1-C4</f>
-        <v>4.5599999999999996</v>
-      </c>
-      <c r="E4">
-        <f>D4/B4</f>
-        <v>0.91199999999999992</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
+      <c r="B8" s="1">
+        <v>100</v>
+      </c>
+      <c r="C8" s="1">
+        <v>1.86</v>
+      </c>
+      <c r="D8" s="1">
+        <f>$A$36-C8</f>
+        <v>3.1399999999999997</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="0"/>
+        <v>3.1399999999999997E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>110</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1.855</v>
+      </c>
+      <c r="D9" s="1">
+        <f>$A$36-C9</f>
+        <v>3.145</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" si="0"/>
+        <v>2.859090909090909E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>200</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2.04</v>
+      </c>
+      <c r="D10" s="1">
+        <f>$A$36-C10</f>
+        <v>2.96</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="0"/>
+        <v>1.4800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>220</v>
+      </c>
+      <c r="C11" s="1">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="D11" s="1">
+        <f>$A$36-C11</f>
+        <v>2.93</v>
+      </c>
+      <c r="E11" s="1">
+        <f t="shared" si="0"/>
+        <v>1.3318181818181819E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>320</v>
+      </c>
+      <c r="C12" s="1">
+        <v>2.15</v>
+      </c>
+      <c r="D12" s="1">
+        <f>$A$36-C12</f>
+        <v>2.85</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="0"/>
+        <v>8.906250000000001E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>10</v>
       </c>
-      <c r="C5">
-        <v>0.81</v>
-      </c>
-      <c r="D5">
-        <f>$A$1-C5</f>
-        <v>4.1899999999999995</v>
-      </c>
-      <c r="E5">
-        <f>D5/B5</f>
-        <v>0.41899999999999993</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6">
+      <c r="B13" s="1">
+        <v>330</v>
+      </c>
+      <c r="C13" s="1">
+        <v>2.06</v>
+      </c>
+      <c r="D13" s="1">
+        <f>$A$36-C13</f>
+        <v>2.94</v>
+      </c>
+      <c r="E13" s="1">
+        <f t="shared" si="0"/>
+        <v>8.9090909090909082E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>430</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="D14" s="1">
+        <f>$A$36-C14</f>
+        <v>2.8</v>
+      </c>
+      <c r="E14" s="1">
+        <f t="shared" si="0"/>
+        <v>6.5116279069767436E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>440</v>
+      </c>
+      <c r="C15" s="1">
+        <v>2.17</v>
+      </c>
+      <c r="D15" s="1">
+        <f>$A$36-C15</f>
+        <v>2.83</v>
+      </c>
+      <c r="E15" s="1">
+        <f t="shared" si="0"/>
+        <v>6.4318181818181818E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1">
+        <v>500</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="D16" s="1">
+        <f>$A$36-C16</f>
+        <v>2.82</v>
+      </c>
+      <c r="E16" s="1">
+        <f t="shared" si="0"/>
+        <v>5.64E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>510</v>
+      </c>
+      <c r="C17" s="1">
+        <v>2.17</v>
+      </c>
+      <c r="D17" s="1">
+        <f>$A$36-C17</f>
+        <v>2.83</v>
+      </c>
+      <c r="E17" s="1">
+        <f t="shared" si="0"/>
+        <v>5.5490196078431375E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>15</v>
+      </c>
+      <c r="B18" s="1">
+        <v>550</v>
+      </c>
+      <c r="C18" s="1">
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="D18" s="1">
+        <f>$A$36-C18</f>
+        <v>2.76</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="0"/>
+        <v>5.0181818181818175E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>16</v>
+      </c>
+      <c r="B19" s="1">
+        <v>610</v>
+      </c>
+      <c r="C19" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="D19" s="1">
+        <f>$A$36-C19</f>
+        <v>2.75</v>
+      </c>
+      <c r="E19" s="1">
+        <f t="shared" si="0"/>
+        <v>4.5081967213114757E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1">
+        <v>660</v>
+      </c>
+      <c r="C20" s="1">
+        <v>2.29</v>
+      </c>
+      <c r="D20" s="1">
+        <f>$A$36-C20</f>
+        <v>2.71</v>
+      </c>
+      <c r="E20" s="1">
+        <f t="shared" si="0"/>
+        <v>4.1060606060606061E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>18</v>
+      </c>
+      <c r="B21" s="1">
+        <v>710</v>
+      </c>
+      <c r="C21" s="1">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="D21" s="1">
+        <f>$A$36-C21</f>
+        <v>2.74</v>
+      </c>
+      <c r="E21" s="1">
+        <f t="shared" si="0"/>
+        <v>3.859154929577465E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>19</v>
+      </c>
+      <c r="B22" s="1">
+        <v>760</v>
+      </c>
+      <c r="C22" s="1">
+        <v>2.2599999999999998</v>
+      </c>
+      <c r="D22" s="1">
+        <f>$A$36-C22</f>
+        <v>2.74</v>
+      </c>
+      <c r="E22" s="1">
+        <f t="shared" si="0"/>
+        <v>3.6052631578947373E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
         <v>20</v>
       </c>
-      <c r="C6">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="D6">
-        <f>$A$1-C6</f>
-        <v>3.87</v>
-      </c>
-      <c r="E6">
-        <f>D6/B6</f>
-        <v>0.19350000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>50</v>
-      </c>
-      <c r="C7">
-        <v>1.64</v>
-      </c>
-      <c r="D7">
-        <f>$A$1-C7</f>
-        <v>3.3600000000000003</v>
-      </c>
-      <c r="E7">
-        <f>D7/B7</f>
-        <v>6.720000000000001E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="B23" s="1">
+        <v>860</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2.33</v>
+      </c>
+      <c r="D23" s="1">
+        <f>$A$36-C23</f>
+        <v>2.67</v>
+      </c>
+      <c r="E23" s="1">
+        <f t="shared" si="0"/>
+        <v>3.1046511627906975E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>21</v>
+      </c>
+      <c r="B24" s="1">
+        <v>930</v>
+      </c>
+      <c r="C24" s="1">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D24" s="1">
+        <f>$A$36-C24</f>
+        <v>2.7</v>
+      </c>
+      <c r="E24" s="1">
+        <f t="shared" si="0"/>
+        <v>2.9032258064516131E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>22</v>
+      </c>
+      <c r="B25" s="1">
+        <v>980</v>
+      </c>
+      <c r="C25" s="1">
+        <v>2.33</v>
+      </c>
+      <c r="D25" s="1">
+        <f>$A$36-C25</f>
+        <v>2.67</v>
+      </c>
+      <c r="E25" s="1">
+        <f t="shared" si="0"/>
+        <v>2.7244897959183673E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>23</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1000</v>
+      </c>
+      <c r="C26" s="1">
+        <v>2.25</v>
+      </c>
+      <c r="D26" s="1">
+        <f>$A$36-C26</f>
+        <v>2.75</v>
+      </c>
+      <c r="E26" s="1">
+        <f t="shared" si="0"/>
+        <v>2.7499999999999998E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>24</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1100</v>
+      </c>
+      <c r="C27" s="1">
+        <v>2.31</v>
+      </c>
+      <c r="D27" s="1">
+        <f>$A$36-C27</f>
+        <v>2.69</v>
+      </c>
+      <c r="E27" s="1">
+        <f t="shared" si="0"/>
+        <v>2.4454545454545454E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>25</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1330</v>
+      </c>
+      <c r="C28" s="1">
+        <v>2.37</v>
+      </c>
+      <c r="D28" s="1">
+        <f>$A$36-C28</f>
+        <v>2.63</v>
+      </c>
+      <c r="E28" s="1">
+        <f t="shared" si="0"/>
+        <v>1.9774436090225565E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>26</v>
+      </c>
+      <c r="B29" s="1">
+        <v>2000</v>
+      </c>
+      <c r="C29" s="1">
+        <v>2.37</v>
+      </c>
+      <c r="D29" s="1">
+        <f>$A$36-C29</f>
+        <v>2.63</v>
+      </c>
+      <c r="E29" s="1">
+        <f t="shared" si="0"/>
+        <v>1.315E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>27</v>
+      </c>
+      <c r="B30" s="1">
+        <v>5000</v>
+      </c>
+      <c r="C30" s="1">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="D30" s="1">
+        <f>$A$36-C30</f>
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="E30" s="1">
+        <f t="shared" si="0"/>
+        <v>5.0999999999999993E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>28</v>
+      </c>
+      <c r="B31" s="1">
+        <v>5330</v>
+      </c>
+      <c r="C31" s="1">
+        <v>2.4</v>
+      </c>
+      <c r="D31" s="1">
+        <f>$A$36-C31</f>
+        <v>2.6</v>
+      </c>
+      <c r="E31" s="1">
+        <f t="shared" si="0"/>
+        <v>4.8780487804878049E-4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>29</v>
+      </c>
+      <c r="B32" s="1">
+        <v>100000</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2.58</v>
+      </c>
+      <c r="D32" s="1">
+        <f>$A$36-C32</f>
+        <v>2.42</v>
+      </c>
+      <c r="E32" s="1">
+        <f t="shared" si="0"/>
+        <v>2.4199999999999999E-5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>30</v>
+      </c>
+      <c r="B33" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2.68</v>
+      </c>
+      <c r="D33" s="1">
+        <f>$A$36-C33</f>
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="E33" s="1">
+        <f t="shared" ref="E33" si="1">D33/B33</f>
+        <v>2.3199999999999998E-6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B8">
-        <v>100</v>
-      </c>
-      <c r="C8">
-        <v>1.86</v>
-      </c>
-      <c r="D8">
-        <f>$A$1-C8</f>
-        <v>3.1399999999999997</v>
-      </c>
-      <c r="E8">
-        <f>D8/B8</f>
-        <v>3.1399999999999997E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>6</v>
-      </c>
-      <c r="B9">
-        <v>110</v>
-      </c>
-      <c r="C9">
-        <v>1.855</v>
-      </c>
-      <c r="D9">
-        <f>$A$1-C9</f>
-        <v>3.145</v>
-      </c>
-      <c r="E9">
-        <f>D9/B9</f>
-        <v>2.859090909090909E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>7</v>
-      </c>
-      <c r="B10">
-        <v>200</v>
-      </c>
-      <c r="C10">
-        <v>2.04</v>
-      </c>
-      <c r="D10">
-        <f>$A$1-C10</f>
-        <v>2.96</v>
-      </c>
-      <c r="E10">
-        <f>D10/B10</f>
-        <v>1.4800000000000001E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11">
-        <v>8</v>
-      </c>
-      <c r="B11">
-        <v>220</v>
-      </c>
-      <c r="C11">
-        <v>2.0699999999999998</v>
-      </c>
-      <c r="D11">
-        <f>$A$1-C11</f>
-        <v>2.93</v>
-      </c>
-      <c r="E11">
-        <f>D11/B11</f>
-        <v>1.3318181818181819E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12">
-        <v>9</v>
-      </c>
-      <c r="B12">
-        <v>320</v>
-      </c>
-      <c r="C12">
-        <v>2.15</v>
-      </c>
-      <c r="D12">
-        <f>$A$1-C12</f>
-        <v>2.85</v>
-      </c>
-      <c r="E12">
-        <f>D12/B12</f>
-        <v>8.906250000000001E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13">
-        <v>10</v>
-      </c>
-      <c r="B13">
-        <v>330</v>
-      </c>
-      <c r="C13">
-        <v>2.06</v>
-      </c>
-      <c r="D13">
-        <f>$A$1-C13</f>
-        <v>2.94</v>
-      </c>
-      <c r="E13">
-        <f>D13/B13</f>
-        <v>8.9090909090909082E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14">
-        <v>11</v>
-      </c>
-      <c r="B14">
-        <v>430</v>
-      </c>
-      <c r="C14">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="D14">
-        <f t="shared" ref="D14:D15" si="0">$A$1-C14</f>
-        <v>2.8</v>
-      </c>
-      <c r="E14">
-        <f>D14/B14</f>
-        <v>6.5116279069767436E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15">
-        <v>12</v>
-      </c>
-      <c r="B15">
-        <v>440</v>
-      </c>
-      <c r="C15">
-        <v>2.17</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="0"/>
-        <v>2.83</v>
-      </c>
-      <c r="E15">
-        <f>D15/B15</f>
-        <v>6.4318181818181818E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>13</v>
-      </c>
-      <c r="B16">
-        <v>500</v>
-      </c>
-      <c r="C16">
-        <v>2.1800000000000002</v>
-      </c>
-      <c r="D16">
-        <f>$A$1-C16</f>
-        <v>2.82</v>
-      </c>
-      <c r="E16">
-        <f>D16/B16</f>
-        <v>5.64E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>14</v>
-      </c>
-      <c r="B17">
-        <v>510</v>
-      </c>
-      <c r="C17">
-        <v>2.17</v>
-      </c>
-      <c r="D17">
-        <f>$A$1-C17</f>
-        <v>2.83</v>
-      </c>
-      <c r="E17">
-        <f>D17/B17</f>
-        <v>5.5490196078431375E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>15</v>
-      </c>
-      <c r="B18">
-        <v>550</v>
-      </c>
-      <c r="C18">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="D18">
-        <f>$A$1-C18</f>
-        <v>2.76</v>
-      </c>
-      <c r="E18">
-        <f>D18/B18</f>
-        <v>5.0181818181818175E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>16</v>
-      </c>
-      <c r="B19">
-        <v>610</v>
-      </c>
-      <c r="C19">
-        <v>2.25</v>
-      </c>
-      <c r="D19">
-        <f>$A$1-C19</f>
-        <v>2.75</v>
-      </c>
-      <c r="E19">
-        <f>D19/B19</f>
-        <v>4.5081967213114757E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>17</v>
-      </c>
-      <c r="B20">
-        <v>660</v>
-      </c>
-      <c r="C20">
-        <v>2.29</v>
-      </c>
-      <c r="D20">
-        <f>$A$1-C20</f>
-        <v>2.71</v>
-      </c>
-      <c r="E20">
-        <f>D20/B20</f>
-        <v>4.1060606060606061E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>18</v>
-      </c>
-      <c r="B21">
-        <v>710</v>
-      </c>
-      <c r="C21">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="D21">
-        <f>$A$1-C21</f>
-        <v>2.74</v>
-      </c>
-      <c r="E21">
-        <f>D21/B21</f>
-        <v>3.859154929577465E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>19</v>
-      </c>
-      <c r="B22">
-        <v>760</v>
-      </c>
-      <c r="C22">
-        <v>2.2599999999999998</v>
-      </c>
-      <c r="D22">
-        <f>$A$1-C22</f>
-        <v>2.74</v>
-      </c>
-      <c r="E22">
-        <f>D22/B22</f>
-        <v>3.6052631578947373E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>20</v>
-      </c>
-      <c r="B23">
-        <v>860</v>
-      </c>
-      <c r="C23">
-        <v>2.33</v>
-      </c>
-      <c r="D23">
-        <f>$A$1-C23</f>
-        <v>2.67</v>
-      </c>
-      <c r="E23">
-        <f>D23/B23</f>
-        <v>3.1046511627906975E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>21</v>
-      </c>
-      <c r="B24">
-        <v>930</v>
-      </c>
-      <c r="C24">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="D24">
-        <f>$A$1-C24</f>
-        <v>2.7</v>
-      </c>
-      <c r="E24">
-        <f>D24/B24</f>
-        <v>2.9032258064516131E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>22</v>
-      </c>
-      <c r="B25">
-        <v>980</v>
-      </c>
-      <c r="C25">
-        <v>2.33</v>
-      </c>
-      <c r="D25">
-        <f>$A$1-C25</f>
-        <v>2.67</v>
-      </c>
-      <c r="E25">
-        <f>D25/B25</f>
-        <v>2.7244897959183673E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>23</v>
-      </c>
-      <c r="B26">
-        <v>1000</v>
-      </c>
-      <c r="C26">
-        <v>2.25</v>
-      </c>
-      <c r="D26">
-        <f>$A$1-C26</f>
-        <v>2.75</v>
-      </c>
-      <c r="E26">
-        <f>D26/B26</f>
-        <v>2.7499999999999998E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>24</v>
-      </c>
-      <c r="B27">
-        <v>1100</v>
-      </c>
-      <c r="C27">
-        <v>2.31</v>
-      </c>
-      <c r="D27">
-        <f>$A$1-C27</f>
-        <v>2.69</v>
-      </c>
-      <c r="E27">
-        <f>D27/B27</f>
-        <v>2.4454545454545454E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>25</v>
-      </c>
-      <c r="B28">
-        <v>1330</v>
-      </c>
-      <c r="C28">
-        <v>2.37</v>
-      </c>
-      <c r="D28">
-        <f>$A$1-C28</f>
-        <v>2.63</v>
-      </c>
-      <c r="E28">
-        <f>D28/B28</f>
-        <v>1.9774436090225565E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>26</v>
-      </c>
-      <c r="B29">
-        <v>2000</v>
-      </c>
-      <c r="C29">
-        <v>2.37</v>
-      </c>
-      <c r="D29">
-        <f>$A$1-C29</f>
-        <v>2.63</v>
-      </c>
-      <c r="E29">
-        <f>D29/B29</f>
-        <v>1.315E-3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>27</v>
-      </c>
-      <c r="B30">
-        <v>5000</v>
-      </c>
-      <c r="C30">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="D30">
-        <f>$A$1-C30</f>
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="E30">
-        <f>D30/B30</f>
-        <v>5.0999999999999993E-4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>28</v>
-      </c>
-      <c r="B31">
-        <v>5330</v>
-      </c>
-      <c r="C31">
-        <v>2.4</v>
-      </c>
-      <c r="D31">
-        <f>$A$1-C31</f>
-        <v>2.6</v>
-      </c>
-      <c r="E31">
-        <f>D31/B31</f>
-        <v>4.8780487804878049E-4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>29</v>
-      </c>
-      <c r="B32">
-        <v>100000</v>
-      </c>
-      <c r="C32">
-        <v>2.58</v>
-      </c>
-      <c r="D32">
-        <f>$A$1-C32</f>
-        <v>2.42</v>
-      </c>
-      <c r="E32">
-        <f>D32/B32</f>
-        <v>2.4199999999999999E-5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>30</v>
-      </c>
-      <c r="B33">
-        <v>1000000</v>
-      </c>
-      <c r="C33">
-        <v>2.68</v>
-      </c>
-      <c r="D33">
-        <f>$A$1-C33</f>
-        <v>2.3199999999999998</v>
-      </c>
-      <c r="E33">
-        <f t="shared" ref="E30:E33" si="1">D33/B33</f>
-        <v>2.3199999999999998E-6</v>
-      </c>
+      <c r="B35" s="3"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <v>5</v>
+      </c>
+      <c r="B36" s="4"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
